--- a/planilhas_participantes/fase_de_grupos/jogador_fase_grupos.xlsx
+++ b/planilhas_participantes/fase_de_grupos/jogador_fase_grupos.xlsx
@@ -2141,15 +2141,11 @@
       <c r="E34" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="F34" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="18" t="n">
-        <v>2</v>
-      </c>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
       <c r="H34" s="19" t="str">
         <f aca="false">IF(OR(ISBLANK(F34) , ISBLANK(G34)),"?",IF(F34&gt;G34,D34,IF(G34&gt;F34,E34,"EMPATE")))</f>
-        <v>Ivory Coast</v>
+        <v>?</v>
       </c>
       <c r="I34" s="11"/>
       <c r="J34" s="11"/>
@@ -2613,15 +2609,11 @@
       <c r="E47" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="F47" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="G47" s="18" t="n">
-        <v>0</v>
-      </c>
+      <c r="F47" s="18"/>
+      <c r="G47" s="18"/>
       <c r="H47" s="19" t="str">
         <f aca="false">IF(OR(ISBLANK(F47) , ISBLANK(G47)),"?",IF(F47&gt;G47,D47,IF(G47&gt;F47,E47,"EMPATE")))</f>
-        <v>Spain</v>
+        <v>?</v>
       </c>
       <c r="I47" s="11"/>
       <c r="J47" s="11"/>
